--- a/Summary table of final performance.xlsx
+++ b/Summary table of final performance.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\publ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C4C79D-53D3-4C2B-986A-0325AC3D349A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B567B802-E455-4DE9-BCC1-76960C97EA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="1095" windowWidth="21600" windowHeight="11295" xr2:uid="{3C4FBCAA-7066-418F-BC54-248374CB77F6}"/>
+    <workbookView xWindow="4200" yWindow="2025" windowWidth="21600" windowHeight="11295" xr2:uid="{3C4FBCAA-7066-418F-BC54-248374CB77F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary table of vendors" sheetId="1" r:id="rId1"/>
-    <sheet name="The final effectiveness of prot" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="26">
   <si>
     <t>Run</t>
   </si>
@@ -63,9 +62,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>100.0%</t>
-  </si>
-  <si>
     <t>Cisco</t>
   </si>
   <si>
@@ -73,18 +69,6 @@
   </si>
   <si>
     <t>Mikrotik</t>
-  </si>
-  <si>
-    <t>80.0%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>5.1%</t>
-  </si>
-  <si>
-    <t>6.9%</t>
   </si>
   <si>
     <t>Vendor</t>
@@ -114,37 +98,22 @@
     <t>Number of blocked attacks</t>
   </si>
   <si>
-    <t>10 blocked out of 10 conducted</t>
+    <t>30 blocked out of 30 conducted</t>
   </si>
   <si>
-    <t>8 blocked out of 10 conducted</t>
+    <t>28 blocked out of 30 conducted</t>
   </si>
   <si>
-    <t>Average detection time</t>
+    <t>24 blocked out of 30 conducted</t>
   </si>
   <si>
-    <t>Average CPU gain</t>
+    <t>Average detection time, ms</t>
   </si>
   <si>
-    <t>Average delay</t>
+    <t>Average CPU gain, %</t>
   </si>
   <si>
-    <t>418 ms</t>
-  </si>
-  <si>
-    <t>655 ms</t>
-  </si>
-  <si>
-    <t>1858 ms</t>
-  </si>
-  <si>
-    <t>1,35 ms</t>
-  </si>
-  <si>
-    <t>1,34 ms</t>
-  </si>
-  <si>
-    <t>1,44 ms</t>
+    <t>Average delay, ms</t>
   </si>
 </sst>
 </file>
@@ -204,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -222,6 +191,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -558,12 +533,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6231EC80-307D-4A15-AD74-4632FC6D2D25}">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="1"/>
     <col min="7" max="7" width="14.42578125" style="1" customWidth="1"/>
@@ -574,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -603,7 +579,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -626,7 +602,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
@@ -649,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>7</v>
@@ -672,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -695,7 +671,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>7</v>
@@ -718,7 +694,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>7</v>
@@ -741,7 +717,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
@@ -764,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
@@ -787,7 +763,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
@@ -810,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>7</v>
@@ -833,16 +809,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E12" s="3">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F12" s="3">
         <v>3</v>
       </c>
       <c r="G12" s="4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -856,16 +832,16 @@
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F13" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="4">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -879,16 +855,16 @@
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E14" s="3">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="F14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -902,16 +878,16 @@
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E15" s="3">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="F15" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -925,16 +901,16 @@
         <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E16" s="3">
-        <v>389</v>
+        <v>434</v>
       </c>
       <c r="F16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="4">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -948,16 +924,16 @@
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E17" s="3">
-        <v>443</v>
+        <v>396</v>
       </c>
       <c r="F17" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -971,16 +947,16 @@
         <v>6</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E18" s="3">
-        <v>436</v>
+        <v>397</v>
       </c>
       <c r="F18" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -994,13 +970,13 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19" s="3">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="F19" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="4">
         <v>1.35</v>
@@ -1017,16 +993,16 @@
         <v>6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F20" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1040,476 +1016,476 @@
         <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E21" s="3">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F21" s="3">
         <v>3</v>
       </c>
       <c r="G21" s="4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E22" s="3">
+        <v>406</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4</v>
       </c>
       <c r="G22" s="4">
-        <v>1.1200000000000001</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E23" s="3">
+        <v>404</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2</v>
       </c>
       <c r="G23" s="4">
-        <v>1.1499999999999999</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E24" s="3">
+        <v>401</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3</v>
       </c>
       <c r="G24" s="4">
-        <v>1.1100000000000001</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E25" s="3">
+        <v>419</v>
+      </c>
+      <c r="F25" s="3">
+        <v>4</v>
       </c>
       <c r="G25" s="4">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E26" s="3">
+        <v>438</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3</v>
       </c>
       <c r="G26" s="4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E27" s="3">
+        <v>400</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3</v>
       </c>
       <c r="G27" s="4">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E28" s="3">
+        <v>412</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2</v>
       </c>
       <c r="G28" s="4">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E29" s="3">
+        <v>437</v>
+      </c>
+      <c r="F29" s="3">
+        <v>4</v>
       </c>
       <c r="G29" s="4">
-        <v>1.1399999999999999</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E30" s="3">
+        <v>397</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4</v>
       </c>
       <c r="G30" s="4">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E31" s="3">
+        <v>427</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3</v>
       </c>
       <c r="G31" s="4">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E32" s="3">
-        <v>637</v>
+        <v>450</v>
       </c>
       <c r="F32" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="4">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E33" s="3">
-        <v>663</v>
+        <v>436</v>
       </c>
       <c r="F33" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" s="4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E34" s="3">
-        <v>687</v>
+        <v>389</v>
       </c>
       <c r="F34" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G34" s="4">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E35" s="3">
-        <v>671</v>
+        <v>403</v>
       </c>
       <c r="F35" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" s="4">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E36" s="3">
-        <v>654</v>
+        <v>400</v>
       </c>
       <c r="F36" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" s="4">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E37" s="3">
-        <v>628</v>
+        <v>408</v>
       </c>
       <c r="F37" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G37" s="4">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E38" s="3">
-        <v>690</v>
+        <v>398</v>
       </c>
       <c r="F38" s="3">
         <v>4</v>
       </c>
       <c r="G38" s="4">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E39" s="3">
-        <v>653</v>
+        <v>427</v>
       </c>
       <c r="F39" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G39" s="4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E40" s="3">
-        <v>646</v>
+        <v>395</v>
       </c>
       <c r="F40" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" s="4">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E41" s="3">
-        <v>620</v>
+        <v>422</v>
       </c>
       <c r="F41" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G41" s="4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1517,13 +1493,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>7</v>
@@ -1532,7 +1508,7 @@
         <v>7</v>
       </c>
       <c r="G42" s="4">
-        <v>1.05</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1540,13 +1516,13 @@
         <v>2</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>7</v>
@@ -1555,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="G43" s="4">
-        <v>1.1100000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,13 +1539,13 @@
         <v>3</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>7</v>
@@ -1578,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="G44" s="4">
-        <v>1.0900000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1586,13 +1562,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>7</v>
@@ -1601,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="G45" s="4">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1609,13 +1585,13 @@
         <v>5</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>7</v>
@@ -1624,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="G46" s="4">
-        <v>1.1499999999999999</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1632,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>7</v>
@@ -1647,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="G47" s="4">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1655,13 +1631,13 @@
         <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>7</v>
@@ -1670,7 +1646,7 @@
         <v>7</v>
       </c>
       <c r="G48" s="4">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1678,13 +1654,13 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>7</v>
@@ -1693,7 +1669,7 @@
         <v>7</v>
       </c>
       <c r="G49" s="4">
-        <v>1.26</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1701,13 +1677,13 @@
         <v>9</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>7</v>
@@ -1716,7 +1692,7 @@
         <v>7</v>
       </c>
       <c r="G50" s="4">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1724,13 +1700,13 @@
         <v>10</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>7</v>
@@ -1739,7 +1715,7 @@
         <v>7</v>
       </c>
       <c r="G51" s="4">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1747,22 +1723,22 @@
         <v>11</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E52" s="3">
+        <v>626</v>
+      </c>
+      <c r="F52" s="3">
+        <v>5</v>
       </c>
       <c r="G52" s="4">
-        <v>1.1299999999999999</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1770,22 +1746,22 @@
         <v>12</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E53" s="3">
-        <v>1789</v>
+        <v>611</v>
       </c>
       <c r="F53" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G53" s="4">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1793,22 +1769,22 @@
         <v>13</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="E54" s="3">
+        <v>637</v>
+      </c>
+      <c r="F54" s="3">
+        <v>4</v>
       </c>
       <c r="G54" s="4">
-        <v>1.1599999999999999</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1816,22 +1792,22 @@
         <v>14</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E55" s="3">
-        <v>1975</v>
+        <v>678</v>
       </c>
       <c r="F55" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G55" s="4">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -1839,22 +1815,22 @@
         <v>15</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" s="3">
-        <v>2002</v>
-      </c>
-      <c r="F56" s="3">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="G56" s="4">
-        <v>1.47</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1862,22 +1838,22 @@
         <v>16</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E57" s="3">
-        <v>1799</v>
+        <v>664</v>
       </c>
       <c r="F57" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G57" s="4">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -1885,22 +1861,22 @@
         <v>17</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E58" s="3">
-        <v>1896</v>
+        <v>615</v>
       </c>
       <c r="F58" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G58" s="4">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1908,22 +1884,22 @@
         <v>18</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E59" s="3">
-        <v>1806</v>
+        <v>628</v>
       </c>
       <c r="F59" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G59" s="4">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -1931,22 +1907,22 @@
         <v>19</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E60" s="3">
-        <v>1795</v>
+        <v>651</v>
       </c>
       <c r="F60" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G60" s="4">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -1954,121 +1930,1493 @@
         <v>20</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="3">
+        <v>661</v>
+      </c>
+      <c r="F61" s="3">
+        <v>4</v>
+      </c>
+      <c r="G61" s="4">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>21</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="3">
+        <v>626</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4</v>
+      </c>
+      <c r="G62" s="4">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
         <v>22</v>
       </c>
-      <c r="E61" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F61" s="3">
+      <c r="B63" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="3">
+        <v>667</v>
+      </c>
+      <c r="F63" s="3">
+        <v>6</v>
+      </c>
+      <c r="G63" s="4">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>23</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="3">
+        <v>687</v>
+      </c>
+      <c r="F64" s="3">
+        <v>6</v>
+      </c>
+      <c r="G64" s="4">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>24</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="3">
+        <v>687</v>
+      </c>
+      <c r="F65" s="3">
+        <v>4</v>
+      </c>
+      <c r="G65" s="4">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>25</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="3">
+        <v>639</v>
+      </c>
+      <c r="F66" s="3">
+        <v>5</v>
+      </c>
+      <c r="G66" s="4">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>26</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="3">
+        <v>664</v>
+      </c>
+      <c r="F67" s="3">
+        <v>4</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>27</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="3">
+        <v>677</v>
+      </c>
+      <c r="F68" s="3">
+        <v>6</v>
+      </c>
+      <c r="G68" s="4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>28</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="3">
+        <v>698</v>
+      </c>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
+      <c r="G69" s="4">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>29</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="3">
+        <v>619</v>
+      </c>
+      <c r="F70" s="3">
+        <v>4</v>
+      </c>
+      <c r="G70" s="4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>30</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71" s="4">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>31</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="3">
+        <v>614</v>
+      </c>
+      <c r="F72" s="3">
+        <v>6</v>
+      </c>
+      <c r="G72" s="4">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>32</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="3">
+        <v>617</v>
+      </c>
+      <c r="F73" s="3">
+        <v>6</v>
+      </c>
+      <c r="G73" s="4">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>33</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="3">
+        <v>665</v>
+      </c>
+      <c r="F74" s="3">
+        <v>5</v>
+      </c>
+      <c r="G74" s="4">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>34</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="3">
+        <v>629</v>
+      </c>
+      <c r="F75" s="3">
+        <v>6</v>
+      </c>
+      <c r="G75" s="4">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>35</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="3">
+        <v>688</v>
+      </c>
+      <c r="F76" s="3">
+        <v>5</v>
+      </c>
+      <c r="G76" s="4">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>36</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="3">
+        <v>693</v>
+      </c>
+      <c r="F77" s="3">
+        <v>5</v>
+      </c>
+      <c r="G77" s="4">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>37</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="3">
+        <v>621</v>
+      </c>
+      <c r="F78" s="3">
+        <v>5</v>
+      </c>
+      <c r="G78" s="4">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>38</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="3">
+        <v>699</v>
+      </c>
+      <c r="F79" s="3">
+        <v>6</v>
+      </c>
+      <c r="G79" s="4">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>39</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="3">
+        <v>628</v>
+      </c>
+      <c r="F80" s="3">
+        <v>6</v>
+      </c>
+      <c r="G80" s="4">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>40</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="3">
+        <v>676</v>
+      </c>
+      <c r="F81" s="3">
+        <v>6</v>
+      </c>
+      <c r="G81" s="4">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>1</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G82" s="4">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>2</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G83" s="4">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" s="4">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>4</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="4">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>5</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G86" s="4">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>6</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G87" s="4">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>7</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88" s="4">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>8</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" s="4">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>9</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" s="4">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
         <v>10</v>
       </c>
-      <c r="G61" s="4">
+      <c r="B91" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" s="4">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>11</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G92" s="4">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>12</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="3">
+        <v>1810</v>
+      </c>
+      <c r="F93" s="3">
+        <v>10</v>
+      </c>
+      <c r="G93" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>13</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1840</v>
+      </c>
+      <c r="F94" s="3">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>14</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1823</v>
+      </c>
+      <c r="F95" s="3">
+        <v>10</v>
+      </c>
+      <c r="G95" s="4">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>15</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1965</v>
+      </c>
+      <c r="F96" s="3">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>16</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="3">
+        <v>1943</v>
+      </c>
+      <c r="F97" s="3">
+        <v>11</v>
+      </c>
+      <c r="G97" s="4">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>17</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="3">
+        <v>1824</v>
+      </c>
+      <c r="F98" s="3">
+        <v>11</v>
+      </c>
+      <c r="G98" s="4">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>18</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" s="4">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>19</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1784</v>
+      </c>
+      <c r="F100" s="3">
+        <v>11</v>
+      </c>
+      <c r="G100" s="4">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>20</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G101" s="4">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>21</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1938</v>
+      </c>
+      <c r="F102" s="3">
+        <v>11</v>
+      </c>
+      <c r="G102" s="4">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>22</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="3">
+        <v>1801</v>
+      </c>
+      <c r="F103" s="3">
+        <v>8</v>
+      </c>
+      <c r="G103" s="4">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>23</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="3">
+        <v>1820</v>
+      </c>
+      <c r="F104" s="3">
+        <v>8</v>
+      </c>
+      <c r="G104" s="4">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>24</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" s="3">
+        <v>1999</v>
+      </c>
+      <c r="F105" s="3">
+        <v>8</v>
+      </c>
+      <c r="G105" s="4">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>25</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106" s="4">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>26</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="3">
+        <v>2009</v>
+      </c>
+      <c r="F107" s="3">
+        <v>8</v>
+      </c>
+      <c r="G107" s="4">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>27</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="3">
+        <v>1886</v>
+      </c>
+      <c r="F108" s="3">
+        <v>10</v>
+      </c>
+      <c r="G108" s="4">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>28</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="3">
+        <v>1864</v>
+      </c>
+      <c r="F109" s="3">
+        <v>9</v>
+      </c>
+      <c r="G109" s="4">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>29</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G110" s="4">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>30</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G111" s="4">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>31</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G112" s="4">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>32</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" s="4">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>33</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" s="3">
+        <v>1946</v>
+      </c>
+      <c r="F114" s="3">
+        <v>8</v>
+      </c>
+      <c r="G114" s="4">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>34</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" s="3">
+        <v>1932</v>
+      </c>
+      <c r="F115" s="3">
+        <v>11</v>
+      </c>
+      <c r="G115" s="4">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>35</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116" s="3">
+        <v>1794</v>
+      </c>
+      <c r="F116" s="3">
+        <v>8</v>
+      </c>
+      <c r="G116" s="4">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>36</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" s="3">
+        <v>1921</v>
+      </c>
+      <c r="F117" s="3">
+        <v>9</v>
+      </c>
+      <c r="G117" s="4">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>37</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" s="3">
+        <v>1919</v>
+      </c>
+      <c r="F118" s="3">
+        <v>11</v>
+      </c>
+      <c r="G118" s="4">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>38</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="3">
+        <v>1999</v>
+      </c>
+      <c r="F119" s="3">
+        <v>9</v>
+      </c>
+      <c r="G119" s="4">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>39</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="3">
+        <v>1964</v>
+      </c>
+      <c r="F120" s="3">
+        <v>8</v>
+      </c>
+      <c r="G120" s="4">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>40</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="3">
+        <v>1821</v>
+      </c>
+      <c r="F121" s="3">
+        <v>11</v>
+      </c>
+      <c r="G121" s="4">
         <v>1.53</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043F58B6-49DA-40AC-8DFC-CBB1BEAC4AB4}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="124" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D124" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E124" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="F124" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="7">
+        <v>1</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" s="3">
+        <f>AVERAGE(E12:E41)</f>
+        <v>412.5</v>
+      </c>
+      <c r="E125" s="4">
+        <f>AVERAGE(F12:F41)</f>
+        <v>3.1333333333333333</v>
+      </c>
+      <c r="F125" s="4">
+        <f>AVERAGE(G12:G41)</f>
+        <v>1.3513333333333335</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B126" s="8">
+        <f>28/30</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="4">
+        <f>AVERAGE(E52:E55,E57:E70,E72:E81)</f>
+        <v>652.32142857142856</v>
+      </c>
+      <c r="E126" s="4">
+        <f>AVERAGE(F52:F55,F57:F70,F72:F81)</f>
+        <v>5.1071428571428568</v>
+      </c>
+      <c r="F126" s="4">
+        <f>AVERAGE(G52:G81)</f>
+        <v>1.3363333333333336</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>35</v>
+      <c r="B127" s="8">
+        <f>24/30</f>
+        <v>0.8</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" s="4">
+        <f>AVERAGE(E93:E98,E100,E102:E105,E108:E109,E114:E121)</f>
+        <v>1885.3809523809523</v>
+      </c>
+      <c r="E127" s="4">
+        <f>AVERAGE(F93:F98,F100,F102:F105,F107:F109,F114:F121)</f>
+        <v>9.545454545454545</v>
+      </c>
+      <c r="F127" s="4">
+        <f>AVERAGE(G93:G121)</f>
+        <v>1.432758620689655</v>
       </c>
     </row>
   </sheetData>
